--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20211.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -70,7 +70,7 @@
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -79,10 +79,13 @@
     <t>FIGUEROA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ROCHA</t>
@@ -91,16 +94,22 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
-    <t>EDGAR FLORENCIO</t>
+    <t>OSVALDO</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
     <t>ORLANDO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -501,19 +510,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -566,16 +575,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -628,19 +640,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +662,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -688,10 +700,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -700,21 +712,21 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920006</v>
+        <v>21330051920026</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -723,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -734,10 +746,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -746,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -757,10 +769,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -769,7 +781,30 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920012</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20211.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,51 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ORLANDO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -575,7 +530,7 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -587,7 +542,7 @@
         <v>75</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -643,13 +598,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>7.4</v>
@@ -662,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -692,121 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920003</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920026</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920002</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920291</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920012</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
